--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_individual_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_individual_h_8.xlsx
@@ -658,7 +658,7 @@
         <v>0.008490693911309379</v>
       </c>
       <c r="C2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>35641723</v>
+        <v>4031595</v>
       </c>
       <c r="L2" t="n">
-        <v>20082805</v>
+        <v>1977400</v>
       </c>
       <c r="M2" t="n">
-        <v>4894694</v>
+        <v>419663</v>
       </c>
       <c r="N2" t="n">
-        <v>231529</v>
+        <v>12010</v>
       </c>
       <c r="O2" t="n">
-        <v>2885956</v>
+        <v>241698</v>
       </c>
       <c r="P2" t="n">
-        <v>1135918</v>
+        <v>96426</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999936819076538</v>
+        <v>0.9999970197677612</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8761179447174072</v>
+        <v>0.7828881144523621</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7570902705192566</v>
+        <v>0.5974760055541992</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6995456218719482</v>
+        <v>0.4949685037136078</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3211501240730286</v>
+        <v>0.09120803326368332</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7492492198944092</v>
+        <v>0.5523945093154907</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8381680250167847</v>
+        <v>0.6873382925987244</v>
       </c>
       <c r="X2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>38435590</v>
+        <v>4776143</v>
       </c>
       <c r="AG2" t="n">
-        <v>23824653</v>
+        <v>2997819</v>
       </c>
       <c r="AH2" t="n">
-        <v>6405435</v>
+        <v>803798</v>
       </c>
       <c r="AI2" t="n">
-        <v>472232</v>
+        <v>59153</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3675525</v>
+        <v>460411</v>
       </c>
       <c r="AK2" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9562234282493591</v>
+        <v>0.9553927183151245</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114547371864319</v>
+        <v>0.9118788242340088</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582150936126709</v>
+        <v>0.85825514793396</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6619678735733032</v>
+        <v>0.661193311214447</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020171165466309</v>
+        <v>0.9019849300384521</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314440488815308</v>
+        <v>0.9314650297164917</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002034640386319406</v>
       </c>
       <c r="C3" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>35641723</v>
+        <v>4031595</v>
       </c>
       <c r="E3" t="n">
-        <v>4380870</v>
+        <v>918979</v>
       </c>
       <c r="F3" t="n">
-        <v>102559</v>
+        <v>33521</v>
       </c>
       <c r="G3" t="n">
-        <v>8911</v>
+        <v>2424</v>
       </c>
       <c r="H3" t="n">
-        <v>5539</v>
+        <v>2034</v>
       </c>
       <c r="I3" t="n">
-        <v>310</v>
+        <v>125</v>
       </c>
       <c r="J3" t="n">
-        <v>80132658</v>
+        <v>10016603</v>
       </c>
       <c r="K3" t="n">
-        <v>85457129</v>
+        <v>10222867</v>
       </c>
       <c r="L3" t="n">
-        <v>98009439</v>
+        <v>11701500</v>
       </c>
       <c r="M3" t="n">
-        <v>121063714</v>
+        <v>14963465</v>
       </c>
       <c r="N3" t="n">
-        <v>129433333</v>
+        <v>16120329</v>
       </c>
       <c r="O3" t="n">
-        <v>125593819</v>
+        <v>15622859</v>
       </c>
       <c r="P3" t="n">
-        <v>128870357</v>
+        <v>16092147</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8879358768463135</v>
+        <v>0.8081480264663696</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7669916749000549</v>
+        <v>0.5999554991722107</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6551750898361206</v>
+        <v>0.4474305510520935</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3242435157299042</v>
+        <v>0.1340342015028</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7078383564949036</v>
+        <v>0.4730892777442932</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7342135906219482</v>
+        <v>0.4980939030647278</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>38435590</v>
+        <v>4776143</v>
       </c>
       <c r="Z3" t="n">
-        <v>1581425</v>
+        <v>197221</v>
       </c>
       <c r="AA3" t="n">
-        <v>68001</v>
+        <v>8441</v>
       </c>
       <c r="AB3" t="n">
-        <v>54459</v>
+        <v>6838</v>
       </c>
       <c r="AC3" t="n">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>80132976</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>88737218</v>
+        <v>11117918</v>
       </c>
       <c r="AG3" t="n">
-        <v>102138438</v>
+        <v>12743989</v>
       </c>
       <c r="AH3" t="n">
-        <v>122107746</v>
+        <v>15258909</v>
       </c>
       <c r="AI3" t="n">
-        <v>129681597</v>
+        <v>16209685</v>
       </c>
       <c r="AJ3" t="n">
-        <v>126160401</v>
+        <v>15768676</v>
       </c>
       <c r="AK3" t="n">
-        <v>128983636</v>
+        <v>16122748</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575390219688416</v>
+        <v>0.9573953747749329</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098982810974121</v>
+        <v>0.909557044506073</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573940396308899</v>
+        <v>0.8569823503494263</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6613346934318542</v>
+        <v>0.6601602435112</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014958739280701</v>
+        <v>0.9011887311935425</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312471747398376</v>
+        <v>0.9310656785964966</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03209056867736627</v>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>4727622</v>
+        <v>1036071</v>
       </c>
       <c r="E4" t="n">
-        <v>20082805</v>
+        <v>1977400</v>
       </c>
       <c r="F4" t="n">
-        <v>1198080</v>
+        <v>232057</v>
       </c>
       <c r="G4" t="n">
-        <v>59829</v>
+        <v>18242</v>
       </c>
       <c r="H4" t="n">
-        <v>106312</v>
+        <v>29085</v>
       </c>
       <c r="I4" t="n">
-        <v>9192</v>
+        <v>3056</v>
       </c>
       <c r="J4" t="n">
-        <v>318</v>
+        <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>5039698</v>
+        <v>1118049</v>
       </c>
       <c r="L4" t="n">
-        <v>6443497</v>
+        <v>1332189</v>
       </c>
       <c r="M4" t="n">
-        <v>2102268</v>
+        <v>428195</v>
       </c>
       <c r="N4" t="n">
-        <v>489408</v>
+        <v>119667</v>
       </c>
       <c r="O4" t="n">
-        <v>965841</v>
+        <v>195848</v>
       </c>
       <c r="P4" t="n">
-        <v>219321</v>
+        <v>43863</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999968409538269</v>
+        <v>0.9999985098838806</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8819873332977295</v>
+        <v>0.7953175902366638</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7620087862014771</v>
+        <v>0.5987131595611572</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6766337752342224</v>
+        <v>0.4700005352497101</v>
       </c>
       <c r="U4" t="n">
-        <v>0.322689414024353</v>
+        <v>0.1085497662425041</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7279554009437561</v>
+        <v>0.5096753239631653</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7827544212341309</v>
+        <v>0.5776104331016541</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1643061</v>
+        <v>208344</v>
       </c>
       <c r="Z4" t="n">
-        <v>23824653</v>
+        <v>2997819</v>
       </c>
       <c r="AA4" t="n">
-        <v>662423</v>
+        <v>82986</v>
       </c>
       <c r="AB4" t="n">
-        <v>44064</v>
+        <v>5563</v>
       </c>
       <c r="AC4" t="n">
-        <v>9119</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>544</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1759609</v>
+        <v>222998</v>
       </c>
       <c r="AG4" t="n">
-        <v>2314498</v>
+        <v>289700</v>
       </c>
       <c r="AH4" t="n">
-        <v>1058236</v>
+        <v>132751</v>
       </c>
       <c r="AI4" t="n">
-        <v>241144</v>
+        <v>30311</v>
       </c>
       <c r="AJ4" t="n">
-        <v>399259</v>
+        <v>50031</v>
       </c>
       <c r="AK4" t="n">
-        <v>106042</v>
+        <v>13262</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568807482719421</v>
+        <v>0.9563930034637451</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106758832931519</v>
+        <v>0.9107164144515991</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578044176101685</v>
+        <v>0.8576182723045349</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6616511344909668</v>
+        <v>0.6606763601303101</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017564058303833</v>
+        <v>0.901586651802063</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313456416130066</v>
+        <v>0.9312652945518494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>210981</v>
+        <v>59701</v>
       </c>
       <c r="E5" t="n">
-        <v>1715354</v>
+        <v>329718</v>
       </c>
       <c r="F5" t="n">
-        <v>4894694</v>
+        <v>419663</v>
       </c>
       <c r="G5" t="n">
-        <v>165263</v>
+        <v>37008</v>
       </c>
       <c r="H5" t="n">
-        <v>443966</v>
+        <v>81221</v>
       </c>
       <c r="I5" t="n">
-        <v>40550</v>
+        <v>10628</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4498250</v>
+        <v>957089</v>
       </c>
       <c r="L5" t="n">
-        <v>6101059</v>
+        <v>1318511</v>
       </c>
       <c r="M5" t="n">
-        <v>2576124</v>
+        <v>518277</v>
       </c>
       <c r="N5" t="n">
-        <v>482530</v>
+        <v>77594</v>
       </c>
       <c r="O5" t="n">
-        <v>1191184</v>
+        <v>269195</v>
       </c>
       <c r="P5" t="n">
-        <v>411204</v>
+        <v>97164</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999975562095642</v>
+        <v>0.9999988079071045</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9269888401031494</v>
+        <v>0.8729217052459717</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9039738178253174</v>
+        <v>0.837675154209137</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9641878008842468</v>
+        <v>0.9420394897460938</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9925599694252014</v>
+        <v>0.9879200458526611</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9834883809089661</v>
+        <v>0.9715214967727661</v>
       </c>
       <c r="W5" t="n">
-        <v>0.995173454284668</v>
+        <v>0.9913637042045593</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>64236</v>
+        <v>8050</v>
       </c>
       <c r="Z5" t="n">
-        <v>683114</v>
+        <v>86223</v>
       </c>
       <c r="AA5" t="n">
-        <v>6405435</v>
+        <v>803798</v>
       </c>
       <c r="AB5" t="n">
-        <v>79701</v>
+        <v>9997</v>
       </c>
       <c r="AC5" t="n">
-        <v>233268</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>5064</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1704383</v>
+        <v>212541</v>
       </c>
       <c r="AG5" t="n">
-        <v>2359211</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>1065383</v>
+        <v>134142</v>
       </c>
       <c r="AI5" t="n">
-        <v>241827</v>
+        <v>30451</v>
       </c>
       <c r="AJ5" t="n">
-        <v>401615</v>
+        <v>50482</v>
       </c>
       <c r="AK5" t="n">
-        <v>106369</v>
+        <v>13345</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734838008880615</v>
+        <v>0.9733282327651978</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642236232757568</v>
+        <v>0.9640045166015625</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837440848350525</v>
+        <v>0.9836558699607849</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963029623031616</v>
+        <v>0.9962790012359619</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938694834709167</v>
+        <v>0.993844747543335</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983740448951721</v>
+        <v>0.9983706474304199</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>90886</v>
+        <v>17029</v>
       </c>
       <c r="E6" t="n">
-        <v>161078</v>
+        <v>23659</v>
       </c>
       <c r="F6" t="n">
-        <v>156730</v>
+        <v>25979</v>
       </c>
       <c r="G6" t="n">
-        <v>231529</v>
+        <v>12010</v>
       </c>
       <c r="H6" t="n">
-        <v>67145</v>
+        <v>9669</v>
       </c>
       <c r="I6" t="n">
-        <v>6624</v>
+        <v>1253</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>51905</v>
+        <v>6568</v>
       </c>
       <c r="Z6" t="n">
-        <v>42831</v>
+        <v>5365</v>
       </c>
       <c r="AA6" t="n">
-        <v>87352</v>
+        <v>11023</v>
       </c>
       <c r="AB6" t="n">
-        <v>472232</v>
+        <v>59153</v>
       </c>
       <c r="AC6" t="n">
-        <v>55891</v>
+        <v>7014</v>
       </c>
       <c r="AD6" t="n">
-        <v>3848</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>9836</v>
+        <v>5147</v>
       </c>
       <c r="E7" t="n">
-        <v>173137</v>
+        <v>54632</v>
       </c>
       <c r="F7" t="n">
-        <v>610028</v>
+        <v>125369</v>
       </c>
       <c r="G7" t="n">
-        <v>235522</v>
+        <v>55246</v>
       </c>
       <c r="H7" t="n">
-        <v>2885956</v>
+        <v>241698</v>
       </c>
       <c r="I7" t="n">
-        <v>162645</v>
+        <v>28801</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>6480</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>237812</v>
+        <v>29968</v>
       </c>
       <c r="AB7" t="n">
-        <v>60794</v>
+        <v>7646</v>
       </c>
       <c r="AC7" t="n">
-        <v>3675525</v>
+        <v>460411</v>
       </c>
       <c r="AD7" t="n">
-        <v>96346</v>
+        <v>12050</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>140</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>101</v>
       </c>
       <c r="E8" t="n">
-        <v>13058</v>
+        <v>5201</v>
       </c>
       <c r="F8" t="n">
-        <v>34871</v>
+        <v>11269</v>
       </c>
       <c r="G8" t="n">
-        <v>19883</v>
+        <v>6747</v>
       </c>
       <c r="H8" t="n">
-        <v>342879</v>
+        <v>73839</v>
       </c>
       <c r="I8" t="n">
-        <v>1135918</v>
+        <v>96426</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2648</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2126</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>100723</v>
+        <v>12636</v>
       </c>
       <c r="AD8" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
